--- a/tests/Fixtures/tracer-sample.xlsx
+++ b/tests/Fixtures/tracer-sample.xlsx
@@ -17,118 +17,118 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="38">
   <si>
+    <t>Resp 10</t>
+  </si>
+  <si>
+    <t>Resp 9</t>
+  </si>
+  <si>
+    <t>Resp 8</t>
+  </si>
+  <si>
+    <t>Resp 7</t>
+  </si>
+  <si>
+    <t>Resp 6</t>
+  </si>
+  <si>
+    <t>Resp 5</t>
+  </si>
+  <si>
+    <t>UGM</t>
+  </si>
+  <si>
+    <t>Resp 4</t>
+  </si>
+  <si>
+    <t>Resp 3</t>
+  </si>
+  <si>
+    <t>Resp 2</t>
+  </si>
+  <si>
+    <t>Resp 1</t>
+  </si>
+  <si>
+    <t>f1774</t>
+  </si>
+  <si>
+    <t>f1773</t>
+  </si>
+  <si>
+    <t>f1772</t>
+  </si>
+  <si>
+    <t>f1771</t>
+  </si>
+  <si>
+    <t>f1770</t>
+  </si>
+  <si>
+    <t>f1769</t>
+  </si>
+  <si>
+    <t>f1768</t>
+  </si>
+  <si>
+    <t>f1767</t>
+  </si>
+  <si>
+    <t>f1766</t>
+  </si>
+  <si>
+    <t>f1765</t>
+  </si>
+  <si>
+    <t>f1764</t>
+  </si>
+  <si>
+    <t>f1763</t>
+  </si>
+  <si>
+    <t>f1762</t>
+  </si>
+  <si>
+    <t>f1761</t>
+  </si>
+  <si>
+    <t>f6</t>
+  </si>
+  <si>
+    <t>f502</t>
+  </si>
+  <si>
+    <t>f505</t>
+  </si>
+  <si>
+    <t>f5d</t>
+  </si>
+  <si>
+    <t>f7a</t>
+  </si>
+  <si>
+    <t>f14</t>
+  </si>
+  <si>
+    <t>f301</t>
+  </si>
+  <si>
+    <t>f15</t>
+  </si>
+  <si>
+    <t>f18c</t>
+  </si>
+  <si>
+    <t>f1101</t>
+  </si>
+  <si>
+    <t>f8</t>
+  </si>
+  <si>
+    <t>nama</t>
+  </si>
+  <si>
     <t>no</t>
-  </si>
-  <si>
-    <t>nama</t>
-  </si>
-  <si>
-    <t>f8</t>
-  </si>
-  <si>
-    <t>f1101</t>
-  </si>
-  <si>
-    <t>f18c</t>
-  </si>
-  <si>
-    <t>f15</t>
-  </si>
-  <si>
-    <t>f301</t>
-  </si>
-  <si>
-    <t>f14</t>
-  </si>
-  <si>
-    <t>f7a</t>
-  </si>
-  <si>
-    <t>f5d</t>
-  </si>
-  <si>
-    <t>f505</t>
-  </si>
-  <si>
-    <t>f502</t>
-  </si>
-  <si>
-    <t>f6</t>
-  </si>
-  <si>
-    <t>f1761</t>
-  </si>
-  <si>
-    <t>f1762</t>
-  </si>
-  <si>
-    <t>f1763</t>
-  </si>
-  <si>
-    <t>f1764</t>
-  </si>
-  <si>
-    <t>f1765</t>
-  </si>
-  <si>
-    <t>f1766</t>
-  </si>
-  <si>
-    <t>f1767</t>
-  </si>
-  <si>
-    <t>f1768</t>
-  </si>
-  <si>
-    <t>f1769</t>
-  </si>
-  <si>
-    <t>f1770</t>
-  </si>
-  <si>
-    <t>f1771</t>
-  </si>
-  <si>
-    <t>f1772</t>
-  </si>
-  <si>
-    <t>f1773</t>
-  </si>
-  <si>
-    <t>f1774</t>
-  </si>
-  <si>
-    <t>Resp 1</t>
-  </si>
-  <si>
-    <t>Resp 2</t>
-  </si>
-  <si>
-    <t>Resp 3</t>
-  </si>
-  <si>
-    <t>Resp 4</t>
-  </si>
-  <si>
-    <t>UGM</t>
-  </si>
-  <si>
-    <t>Resp 5</t>
-  </si>
-  <si>
-    <t>Resp 6</t>
-  </si>
-  <si>
-    <t>Resp 7</t>
-  </si>
-  <si>
-    <t>Resp 8</t>
-  </si>
-  <si>
-    <t>Resp 9</t>
-  </si>
-  <si>
-    <t>Resp 10</t>
   </si>
 </sst>
 </file>
@@ -468,617 +468,537 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:CW13"/>
+  <dimension ref="A1:CW14"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="3" spans="1:101">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1</v>
-      </c>
-      <c r="M3" t="s">
-        <v>2</v>
-      </c>
-      <c r="T3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>6</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>7</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>8</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>9</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>10</v>
-      </c>
-      <c r="BX3" t="s">
+    <row r="4" spans="1:101">
+      <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4" t="s">
+        <v>35</v>
+      </c>
+      <c r="T4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>33</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>31</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>30</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>29</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>28</v>
+      </c>
+      <c r="BP4" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX4" t="s">
+        <v>26</v>
+      </c>
+      <c r="CG4" t="s">
+        <v>25</v>
+      </c>
+      <c r="CJ4" t="s">
+        <v>24</v>
+      </c>
+      <c r="CK4" t="s">
+        <v>23</v>
+      </c>
+      <c r="CL4" t="s">
+        <v>22</v>
+      </c>
+      <c r="CM4" t="s">
+        <v>21</v>
+      </c>
+      <c r="CN4" t="s">
+        <v>20</v>
+      </c>
+      <c r="CO4" t="s">
+        <v>19</v>
+      </c>
+      <c r="CP4" t="s">
+        <v>18</v>
+      </c>
+      <c r="CQ4" t="s">
+        <v>17</v>
+      </c>
+      <c r="CR4" t="s">
+        <v>16</v>
+      </c>
+      <c r="CS4" t="s">
+        <v>15</v>
+      </c>
+      <c r="CT4" t="s">
+        <v>14</v>
+      </c>
+      <c r="CU4" t="s">
+        <v>13</v>
+      </c>
+      <c r="CV4" t="s">
+        <v>12</v>
+      </c>
+      <c r="CW4" t="s">
         <v>11</v>
-      </c>
-      <c r="CG3" t="s">
-        <v>12</v>
-      </c>
-      <c r="CJ3" t="s">
-        <v>13</v>
-      </c>
-      <c r="CK3" t="s">
-        <v>14</v>
-      </c>
-      <c r="CL3" t="s">
-        <v>15</v>
-      </c>
-      <c r="CM3" t="s">
-        <v>16</v>
-      </c>
-      <c r="CN3" t="s">
-        <v>17</v>
-      </c>
-      <c r="CO3" t="s">
-        <v>18</v>
-      </c>
-      <c r="CP3" t="s">
-        <v>19</v>
-      </c>
-      <c r="CQ3" t="s">
-        <v>20</v>
-      </c>
-      <c r="CR3" t="s">
-        <v>21</v>
-      </c>
-      <c r="CS3" t="s">
-        <v>22</v>
-      </c>
-      <c r="CT3" t="s">
-        <v>23</v>
-      </c>
-      <c r="CU3" t="s">
-        <v>24</v>
-      </c>
-      <c r="CV3" t="s">
-        <v>25</v>
-      </c>
-      <c r="CW3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:101">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-      <c r="T4">
-        <v>3</v>
-      </c>
-      <c r="AM4">
-        <v>2</v>
-      </c>
-      <c r="AY4">
-        <v>3</v>
-      </c>
-      <c r="BC4">
-        <v>1</v>
-      </c>
-      <c r="BD4">
-        <v>5</v>
-      </c>
-      <c r="BI4">
-        <v>2</v>
-      </c>
-      <c r="BP4">
-        <v>4500000</v>
-      </c>
-      <c r="BX4">
-        <v>1</v>
-      </c>
-      <c r="CG4">
-        <v>10</v>
-      </c>
-      <c r="CJ4">
-        <v>4</v>
-      </c>
-      <c r="CK4">
-        <v>3</v>
-      </c>
-      <c r="CL4">
-        <v>5</v>
-      </c>
-      <c r="CM4">
-        <v>4</v>
-      </c>
-      <c r="CN4">
-        <v>3</v>
-      </c>
-      <c r="CO4">
-        <v>2</v>
-      </c>
-      <c r="CP4">
-        <v>4</v>
-      </c>
-      <c r="CQ4">
-        <v>3</v>
-      </c>
-      <c r="CR4">
-        <v>5</v>
-      </c>
-      <c r="CS4">
-        <v>4</v>
-      </c>
-      <c r="CT4">
-        <v>4</v>
-      </c>
-      <c r="CU4">
-        <v>3</v>
-      </c>
-      <c r="CV4">
-        <v>3</v>
-      </c>
-      <c r="CW4">
-        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:101">
       <c r="A5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="M5">
         <v>1</v>
       </c>
       <c r="T5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AM5">
         <v>2</v>
       </c>
       <c r="AY5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BC5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BD5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BI5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP5">
-        <v>3200000</v>
+        <v>4500000</v>
       </c>
       <c r="BX5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CG5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CJ5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CK5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CL5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CM5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CN5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CO5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CP5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CQ5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CR5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CS5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CT5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CU5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CV5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CW5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:101">
       <c r="A6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AM6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BC6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BP6">
-        <v>6000000</v>
+        <v>3200000</v>
       </c>
       <c r="BX6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CG6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="CJ6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="CK6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CL6">
         <v>4</v>
       </c>
       <c r="CM6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CN6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CO6">
         <v>3</v>
       </c>
       <c r="CP6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CQ6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CR6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CS6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="CT6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CU6">
         <v>4</v>
       </c>
       <c r="CV6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CW6">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:101">
       <c r="A7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="M7">
-        <v>4</v>
-      </c>
-      <c r="AK7" t="s">
-        <v>31</v>
+        <v>3</v>
+      </c>
+      <c r="T7">
+        <v>4</v>
+      </c>
+      <c r="AM7">
+        <v>1</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>3</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>3</v>
+      </c>
+      <c r="BP7">
+        <v>6000000</v>
+      </c>
+      <c r="BX7">
+        <v>1</v>
+      </c>
+      <c r="CG7">
+        <v>5</v>
       </c>
       <c r="CJ7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CK7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CL7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CN7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CO7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CP7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CQ7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="CR7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CS7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CT7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CU7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CW7">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:101">
       <c r="A8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="M8">
-        <v>5</v>
-      </c>
-      <c r="AY8">
-        <v>12</v>
-      </c>
-      <c r="BC8">
-        <v>4</v>
-      </c>
-      <c r="BD8">
-        <v>2</v>
-      </c>
-      <c r="BI8">
-        <v>1</v>
-      </c>
-      <c r="BP8">
-        <v>2500000</v>
-      </c>
-      <c r="BX8">
-        <v>3</v>
-      </c>
-      <c r="CG8">
-        <v>15</v>
+        <v>4</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>6</v>
       </c>
       <c r="CJ8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CK8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CL8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CM8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CN8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CO8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CP8">
         <v>4</v>
       </c>
       <c r="CQ8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CR8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CS8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CT8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CU8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CV8">
         <v>4</v>
       </c>
       <c r="CW8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:101">
       <c r="A9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="M9">
-        <v>1</v>
-      </c>
-      <c r="T9">
-        <v>2</v>
-      </c>
-      <c r="AM9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AY9">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="BC9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BD9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BI9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP9">
-        <v>3800000</v>
+        <v>2500000</v>
       </c>
       <c r="BX9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CG9">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="CJ9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="CK9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CL9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CM9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CN9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CO9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CP9">
         <v>4</v>
       </c>
       <c r="CQ9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CR9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CS9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="CT9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="CU9">
         <v>4</v>
       </c>
       <c r="CV9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CW9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:101">
       <c r="A10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="M10">
         <v>1</v>
       </c>
       <c r="T10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BC10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BD10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BI10">
         <v>2</v>
       </c>
       <c r="BP10">
-        <v>5100000</v>
+        <v>3800000</v>
       </c>
       <c r="BX10">
         <v>1</v>
       </c>
       <c r="CG10">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="CJ10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CK10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CL10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CM10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CN10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CO10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CP10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CQ10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CR10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CS10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CT10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CU10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CV10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="CW10">
         <v>4</v>
@@ -1086,214 +1006,294 @@
     </row>
     <row r="11" spans="1:101">
       <c r="A11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="M11">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="T11">
+        <v>3</v>
+      </c>
+      <c r="AM11">
+        <v>3</v>
+      </c>
+      <c r="AY11">
+        <v>2</v>
+      </c>
+      <c r="BC11">
+        <v>2</v>
+      </c>
+      <c r="BD11">
+        <v>6</v>
+      </c>
+      <c r="BI11">
+        <v>2</v>
+      </c>
+      <c r="BP11">
+        <v>5100000</v>
+      </c>
+      <c r="BX11">
+        <v>1</v>
+      </c>
+      <c r="CG11">
+        <v>7</v>
       </c>
       <c r="CJ11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CK11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CL11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="CM11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CN11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CO11">
         <v>3</v>
       </c>
       <c r="CP11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CQ11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CR11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="CS11">
         <v>4</v>
       </c>
       <c r="CT11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CU11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CV11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CW11">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:101">
       <c r="A12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="M12">
-        <v>1</v>
-      </c>
-      <c r="T12">
-        <v>1</v>
-      </c>
-      <c r="AM12">
-        <v>2</v>
-      </c>
-      <c r="AY12">
-        <v>5</v>
-      </c>
-      <c r="BC12">
-        <v>3</v>
-      </c>
-      <c r="BD12">
-        <v>3</v>
-      </c>
-      <c r="BI12">
-        <v>1</v>
-      </c>
-      <c r="BP12">
-        <v>4200000</v>
-      </c>
-      <c r="BX12">
-        <v>2</v>
-      </c>
-      <c r="CG12">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="CJ12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CK12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CL12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CM12">
         <v>4</v>
       </c>
       <c r="CN12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CO12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CP12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CQ12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CR12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CS12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CT12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CU12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CW12">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:101">
       <c r="A13">
+        <v>9</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="T13">
+        <v>1</v>
+      </c>
+      <c r="AM13">
+        <v>2</v>
+      </c>
+      <c r="AY13">
+        <v>5</v>
+      </c>
+      <c r="BC13">
+        <v>3</v>
+      </c>
+      <c r="BD13">
+        <v>3</v>
+      </c>
+      <c r="BI13">
+        <v>1</v>
+      </c>
+      <c r="BP13">
+        <v>4200000</v>
+      </c>
+      <c r="BX13">
+        <v>2</v>
+      </c>
+      <c r="CG13">
+        <v>9</v>
+      </c>
+      <c r="CJ13">
+        <v>4</v>
+      </c>
+      <c r="CK13">
+        <v>5</v>
+      </c>
+      <c r="CL13">
+        <v>4</v>
+      </c>
+      <c r="CM13">
+        <v>4</v>
+      </c>
+      <c r="CN13">
+        <v>3</v>
+      </c>
+      <c r="CO13">
+        <v>4</v>
+      </c>
+      <c r="CP13">
+        <v>5</v>
+      </c>
+      <c r="CQ13">
+        <v>4</v>
+      </c>
+      <c r="CR13">
+        <v>4</v>
+      </c>
+      <c r="CS13">
+        <v>5</v>
+      </c>
+      <c r="CT13">
+        <v>4</v>
+      </c>
+      <c r="CU13">
+        <v>3</v>
+      </c>
+      <c r="CV13">
+        <v>5</v>
+      </c>
+      <c r="CW13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:101">
+      <c r="A14">
         <v>10</v>
       </c>
-      <c r="B13" t="s">
-        <v>37</v>
-      </c>
-      <c r="M13">
-        <v>1</v>
-      </c>
-      <c r="T13">
-        <v>5</v>
-      </c>
-      <c r="AM13">
-        <v>2</v>
-      </c>
-      <c r="AY13">
+      <c r="B14" t="s">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="T14">
+        <v>5</v>
+      </c>
+      <c r="AM14">
+        <v>2</v>
+      </c>
+      <c r="AY14">
         <v>8</v>
       </c>
-      <c r="BC13">
-        <v>1</v>
-      </c>
-      <c r="BD13">
+      <c r="BC14">
+        <v>1</v>
+      </c>
+      <c r="BD14">
         <v>7</v>
       </c>
-      <c r="BI13">
-        <v>2</v>
-      </c>
-      <c r="BP13">
+      <c r="BI14">
+        <v>2</v>
+      </c>
+      <c r="BP14">
         <v>3500000</v>
       </c>
-      <c r="BX13">
-        <v>1</v>
-      </c>
-      <c r="CG13">
+      <c r="BX14">
+        <v>1</v>
+      </c>
+      <c r="CG14">
         <v>11</v>
       </c>
-      <c r="CJ13">
-        <v>3</v>
-      </c>
-      <c r="CK13">
-        <v>3</v>
-      </c>
-      <c r="CL13">
-        <v>5</v>
-      </c>
-      <c r="CM13">
-        <v>3</v>
-      </c>
-      <c r="CN13">
-        <v>4</v>
-      </c>
-      <c r="CO13">
-        <v>2</v>
-      </c>
-      <c r="CP13">
-        <v>4</v>
-      </c>
-      <c r="CQ13">
-        <v>5</v>
-      </c>
-      <c r="CR13">
-        <v>5</v>
-      </c>
-      <c r="CS13">
-        <v>4</v>
-      </c>
-      <c r="CT13">
-        <v>3</v>
-      </c>
-      <c r="CU13">
-        <v>4</v>
-      </c>
-      <c r="CV13">
-        <v>4</v>
-      </c>
-      <c r="CW13">
+      <c r="CJ14">
+        <v>3</v>
+      </c>
+      <c r="CK14">
+        <v>3</v>
+      </c>
+      <c r="CL14">
+        <v>5</v>
+      </c>
+      <c r="CM14">
+        <v>3</v>
+      </c>
+      <c r="CN14">
+        <v>4</v>
+      </c>
+      <c r="CO14">
+        <v>2</v>
+      </c>
+      <c r="CP14">
+        <v>4</v>
+      </c>
+      <c r="CQ14">
+        <v>5</v>
+      </c>
+      <c r="CR14">
+        <v>5</v>
+      </c>
+      <c r="CS14">
+        <v>4</v>
+      </c>
+      <c r="CT14">
+        <v>3</v>
+      </c>
+      <c r="CU14">
+        <v>4</v>
+      </c>
+      <c r="CV14">
+        <v>4</v>
+      </c>
+      <c r="CW14">
         <v>3</v>
       </c>
     </row>
